--- a/data/processed/dataset_turismo_clima.xlsx
+++ b/data/processed/dataset_turismo_clima.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/73508a156d1a57ee/Desktop/3! Cuatrimestre/03 - Aprendizaje Automático/03 - Instancia Parcial/parcial/data/processed/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/73508a156d1a57ee/Desktop/3! Cuatrimestre/03 - Aprendizaje Automático/03 - Instancia Parcial/ParciaML_DarioMartinez2026/data/processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_732583695679ECDEE54878D6425DCE3A874CBF21" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CF3A283-4752-4C46-AF11-3AACAB9ECA88}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="11_732583695679ECDEE54878D6425DCE3A874CBF21" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89F86913-DF23-4478-A210-F5EAD816C49F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="127">
   <si>
     <t>fecha</t>
   </si>
@@ -315,6 +316,93 @@
   <si>
     <t>2024/2025</t>
   </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Fecha del registro.</t>
+  </si>
+  <si>
+    <t>Año correspondiente al dato.</t>
+  </si>
+  <si>
+    <t>Número de mes (1 a 12).</t>
+  </si>
+  <si>
+    <t>Nombre o representación alternativa del mes (según cómo se importó el archivo).</t>
+  </si>
+  <si>
+    <t>Total de pernoctaciones (noches de alojamiento) en Ushuaia.</t>
+  </si>
+  <si>
+    <t>Pernoctaciones realizadas por turistas residentes en Argentina.</t>
+  </si>
+  <si>
+    <t>Pernoctaciones realizadas por turistas extranjeros.</t>
+  </si>
+  <si>
+    <t>Total de viajeros que llegaron a establecimientos turísticos de Ushuaia.</t>
+  </si>
+  <si>
+    <t>Cantidad de viajeros residentes en Argentina.</t>
+  </si>
+  <si>
+    <t>Cantidad de viajeros extranjeros.</t>
+  </si>
+  <si>
+    <t>Estadía promedio total (cantidad promedio de noches por viajero).</t>
+  </si>
+  <si>
+    <t>Estadía promedio de turistas residentes.</t>
+  </si>
+  <si>
+    <t>Estadía promedio de turistas extranjeros.</t>
+  </si>
+  <si>
+    <t>Total de visitas al Parque Nacional Tierra del Fuego.</t>
+  </si>
+  <si>
+    <t>Visitas al parque realizadas por residentes.</t>
+  </si>
+  <si>
+    <t>Visitas al parque realizadas por no residentes.</t>
+  </si>
+  <si>
+    <t>Cantidad de habitaciones disponibles en establecimientos hoteleros.</t>
+  </si>
+  <si>
+    <t>Cantidad de habitaciones ocupadas.</t>
+  </si>
+  <si>
+    <t>ush_toh_%</t>
+  </si>
+  <si>
+    <t>Tasa de Ocupación Hotelera (TOH) de habitaciones, expresada en porcentaje.</t>
+  </si>
+  <si>
+    <t>Cantidad de plazas/camas disponibles.</t>
+  </si>
+  <si>
+    <t>Cantidad de plazas/camas ocupadas.</t>
+  </si>
+  <si>
+    <t>ush_top_%</t>
+  </si>
+  <si>
+    <t>Tasa de Ocupación de Plazas (TOP), expresada en porcentaje.</t>
+  </si>
+  <si>
+    <t>Temperatura media mensual (°C) medida a 2 metros del suelo.</t>
+  </si>
+  <si>
+    <t>Precipitación acumulada mensual (mm).</t>
+  </si>
+  <si>
+    <t>Velocidad máxima del viento registrada a 10 metros de altura (km/h o m/s según la fuente).</t>
+  </si>
 </sst>
 </file>
 
@@ -323,7 +411,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -349,8 +437,16 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -393,6 +489,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -421,7 +541,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -450,6 +570,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -30521,4 +30659,226 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BED8266-1D4A-4FB2-97DF-501FCB41EE70}">
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="76.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/processed/dataset_turismo_clima.xlsx
+++ b/data/processed/dataset_turismo_clima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/73508a156d1a57ee/Desktop/3! Cuatrimestre/03 - Aprendizaje Automático/03 - Instancia Parcial/ParciaML_DarioMartinez2026/data/processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="11_732583695679ECDEE54878D6425DCE3A874CBF21" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89F86913-DF23-4478-A210-F5EAD816C49F}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="11_732583695679ECDEE54878D6425DCE3A874CBF21" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA38ABF9-7C44-4B42-AA95-7AF14C5E8DBE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -979,7 +979,7 @@
     <col min="79" max="79" width="29.109375" bestFit="1" customWidth="1"/>
     <col min="80" max="80" width="20.88671875" bestFit="1" customWidth="1"/>
     <col min="81" max="81" width="21.21875" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="22.21875" customWidth="1"/>
     <col min="83" max="83" width="20.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1293,13 +1293,13 @@
         <v>57.261837389171852</v>
       </c>
       <c r="CC2">
-        <v>7.6</v>
+        <v>9.83</v>
       </c>
       <c r="CD2">
-        <v>2.5</v>
+        <v>112.9</v>
       </c>
       <c r="CE2">
-        <v>6.4</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="3" spans="1:83" x14ac:dyDescent="0.3">
@@ -1361,13 +1361,13 @@
         <v>53.821563498982847</v>
       </c>
       <c r="CC3">
-        <v>8.5</v>
+        <v>11.49</v>
       </c>
       <c r="CD3">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="CE3">
-        <v>20.9</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="4" spans="1:83" x14ac:dyDescent="0.3">
@@ -1429,13 +1429,13 @@
         <v>40.626017038384227</v>
       </c>
       <c r="CC4">
-        <v>6.5</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="CD4">
-        <v>12.4</v>
+        <v>58.1</v>
       </c>
       <c r="CE4">
-        <v>8.6</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="5" spans="1:83" x14ac:dyDescent="0.3">
@@ -1497,13 +1497,13 @@
         <v>28.35122242098986</v>
       </c>
       <c r="CC5">
-        <v>8.9</v>
+        <v>5.2</v>
       </c>
       <c r="CD5">
-        <v>0.8</v>
+        <v>53.1</v>
       </c>
       <c r="CE5">
-        <v>10.8</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="6" spans="1:83" x14ac:dyDescent="0.3">
@@ -1565,13 +1565,13 @@
         <v>12.37802550575984</v>
       </c>
       <c r="CC6">
-        <v>-0.4</v>
+        <v>1.57</v>
       </c>
       <c r="CD6">
-        <v>0</v>
+        <v>49.1</v>
       </c>
       <c r="CE6">
-        <v>10.3</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="7" spans="1:83" x14ac:dyDescent="0.3">
@@ -1633,13 +1633,13 @@
         <v>10.58708616080609</v>
       </c>
       <c r="CC7">
-        <v>2.2999999999999998</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="CD7">
-        <v>1.7</v>
+        <v>77.5</v>
       </c>
       <c r="CE7">
-        <v>10.199999999999999</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="8" spans="1:83" x14ac:dyDescent="0.3">
@@ -1701,13 +1701,13 @@
         <v>28.868623266762999</v>
       </c>
       <c r="CC8">
-        <v>-2.9</v>
+        <v>-1.93</v>
       </c>
       <c r="CD8">
-        <v>0.1</v>
+        <v>35.9</v>
       </c>
       <c r="CE8">
-        <v>10.199999999999999</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="9" spans="1:83" x14ac:dyDescent="0.3">
@@ -1769,13 +1769,13 @@
         <v>22.173297383275461</v>
       </c>
       <c r="CC9">
-        <v>-0.2</v>
+        <v>-0.26</v>
       </c>
       <c r="CD9">
-        <v>4</v>
+        <v>30.6</v>
       </c>
       <c r="CE9">
-        <v>10.199999999999999</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:83" x14ac:dyDescent="0.3">
@@ -1837,13 +1837,13 @@
         <v>33.644084732214232</v>
       </c>
       <c r="CC10">
-        <v>0.6</v>
+        <v>0.89</v>
       </c>
       <c r="CD10">
-        <v>0</v>
+        <v>63.1</v>
       </c>
       <c r="CE10">
-        <v>7.2</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="11" spans="1:83" x14ac:dyDescent="0.3">
@@ -1905,13 +1905,13 @@
         <v>30.021594162917019</v>
       </c>
       <c r="CC11">
-        <v>4.9000000000000004</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="CD11">
-        <v>1.2</v>
+        <v>52.3</v>
       </c>
       <c r="CE11">
-        <v>19</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="12" spans="1:83" x14ac:dyDescent="0.3">
@@ -1973,13 +1973,13 @@
         <v>40.467716841695839</v>
       </c>
       <c r="CC12">
-        <v>2.7</v>
+        <v>7.57</v>
       </c>
       <c r="CD12">
-        <v>0</v>
+        <v>75.7</v>
       </c>
       <c r="CE12">
-        <v>10</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="13" spans="1:83" x14ac:dyDescent="0.3">
@@ -2041,13 +2041,13 @@
         <v>39.728551018873603</v>
       </c>
       <c r="CC13">
-        <v>8</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="CD13">
-        <v>1</v>
+        <v>96.3</v>
       </c>
       <c r="CE13">
-        <v>17.600000000000001</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="14" spans="1:83" x14ac:dyDescent="0.3">
@@ -2109,13 +2109,13 @@
         <v>57.892388116792098</v>
       </c>
       <c r="CC14">
-        <v>9.1999999999999993</v>
+        <v>8.6199999999999992</v>
       </c>
       <c r="CD14">
-        <v>0.8</v>
+        <v>91.1</v>
       </c>
       <c r="CE14">
-        <v>20.3</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="15" spans="1:83" x14ac:dyDescent="0.3">
@@ -2177,13 +2177,13 @@
         <v>57.359414063875498</v>
       </c>
       <c r="CC15">
-        <v>10.1</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="CD15">
-        <v>0.4</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="CE15">
-        <v>13.8</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="16" spans="1:83" x14ac:dyDescent="0.3">
@@ -2245,13 +2245,13 @@
         <v>43.627540670617698</v>
       </c>
       <c r="CC16">
-        <v>13.7</v>
+        <v>6.65</v>
       </c>
       <c r="CD16">
-        <v>0</v>
+        <v>53.8</v>
       </c>
       <c r="CE16">
-        <v>14.4</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="17" spans="1:83" x14ac:dyDescent="0.3">
@@ -2313,13 +2313,13 @@
         <v>23.8777982443039</v>
       </c>
       <c r="CC17">
-        <v>5.8</v>
+        <v>3.57</v>
       </c>
       <c r="CD17">
-        <v>0.1</v>
+        <v>79.7</v>
       </c>
       <c r="CE17">
-        <v>13.9</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="18" spans="1:83" x14ac:dyDescent="0.3">
@@ -2381,13 +2381,13 @@
         <v>13.0146325241104</v>
       </c>
       <c r="CC18">
-        <v>1.1000000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="CD18">
-        <v>14.2</v>
+        <v>72.7</v>
       </c>
       <c r="CE18">
-        <v>12</v>
+        <v>16.600000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:83" x14ac:dyDescent="0.3">
@@ -2449,13 +2449,13 @@
         <v>12.216957605985</v>
       </c>
       <c r="CC19">
-        <v>0.9</v>
+        <v>-2.6</v>
       </c>
       <c r="CD19">
-        <v>6</v>
+        <v>21.5</v>
       </c>
       <c r="CE19">
-        <v>8.9</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="20" spans="1:83" x14ac:dyDescent="0.3">
@@ -2517,13 +2517,13 @@
         <v>22.7123270179247</v>
       </c>
       <c r="CC20">
-        <v>-3.5</v>
+        <v>-1.0900000000000001</v>
       </c>
       <c r="CD20">
-        <v>0</v>
+        <v>52.4</v>
       </c>
       <c r="CE20">
-        <v>10.1</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="21" spans="1:83" x14ac:dyDescent="0.3">
@@ -2585,13 +2585,13 @@
         <v>23.854337470178201</v>
       </c>
       <c r="CC21">
-        <v>-2.6</v>
+        <v>-0.87</v>
       </c>
       <c r="CD21">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="CE21">
-        <v>6.8</v>
+        <v>18.399999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:83" x14ac:dyDescent="0.3">
@@ -2653,13 +2653,13 @@
         <v>38.049400365340297</v>
       </c>
       <c r="CC22">
-        <v>0.2</v>
+        <v>2.46</v>
       </c>
       <c r="CD22">
-        <v>0</v>
+        <v>40.1</v>
       </c>
       <c r="CE22">
-        <v>7.9</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="23" spans="1:83" x14ac:dyDescent="0.3">
@@ -2721,13 +2721,13 @@
         <v>34.6172953510208</v>
       </c>
       <c r="CC23">
-        <v>3.4</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="CD23">
-        <v>0</v>
+        <v>54.2</v>
       </c>
       <c r="CE23">
-        <v>11.3</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="24" spans="1:83" x14ac:dyDescent="0.3">
@@ -2789,13 +2789,13 @@
         <v>48.865987339817799</v>
       </c>
       <c r="CC24">
-        <v>7.4</v>
+        <v>7.29</v>
       </c>
       <c r="CD24">
-        <v>1.8</v>
+        <v>115.2</v>
       </c>
       <c r="CE24">
-        <v>19.899999999999999</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="25" spans="1:83" x14ac:dyDescent="0.3">
@@ -2857,13 +2857,13 @@
         <v>43.5361371988567</v>
       </c>
       <c r="CC25">
-        <v>9.1</v>
+        <v>7.91</v>
       </c>
       <c r="CD25">
-        <v>2.2999999999999998</v>
+        <v>110.6</v>
       </c>
       <c r="CE25">
-        <v>19</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="26" spans="1:83" x14ac:dyDescent="0.3">
@@ -2925,13 +2925,13 @@
         <v>63.125362178868102</v>
       </c>
       <c r="CC26">
-        <v>8.6</v>
+        <v>9.48</v>
       </c>
       <c r="CD26">
-        <v>0.3</v>
+        <v>120.9</v>
       </c>
       <c r="CE26">
-        <v>9.5</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="27" spans="1:83" x14ac:dyDescent="0.3">
@@ -2993,13 +2993,13 @@
         <v>57.586988483214903</v>
       </c>
       <c r="CC27">
-        <v>9.9</v>
+        <v>9.34</v>
       </c>
       <c r="CD27">
-        <v>2</v>
+        <v>78.900000000000006</v>
       </c>
       <c r="CE27">
-        <v>17.600000000000001</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="28" spans="1:83" x14ac:dyDescent="0.3">
@@ -3061,13 +3061,13 @@
         <v>40.7691566662997</v>
       </c>
       <c r="CC28">
-        <v>9.4</v>
+        <v>7.43</v>
       </c>
       <c r="CD28">
-        <v>2.2000000000000002</v>
+        <v>50.4</v>
       </c>
       <c r="CE28">
-        <v>11.7</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="29" spans="1:83" x14ac:dyDescent="0.3">
@@ -3129,13 +3129,13 @@
         <v>26.920988324735301</v>
       </c>
       <c r="CC29">
-        <v>5.5</v>
+        <v>3.85</v>
       </c>
       <c r="CD29">
-        <v>7.3</v>
+        <v>89.8</v>
       </c>
       <c r="CE29">
-        <v>22.6</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="30" spans="1:83" x14ac:dyDescent="0.3">
@@ -3197,13 +3197,13 @@
         <v>12.5330441266183</v>
       </c>
       <c r="CC30">
-        <v>6.3</v>
+        <v>2.54</v>
       </c>
       <c r="CD30">
-        <v>0.6</v>
+        <v>62</v>
       </c>
       <c r="CE30">
-        <v>8.5</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="31" spans="1:83" x14ac:dyDescent="0.3">
@@ -3265,13 +3265,13 @@
         <v>9.8893417021150007</v>
       </c>
       <c r="CC31">
-        <v>3.5</v>
+        <v>-0.92</v>
       </c>
       <c r="CD31">
-        <v>8.8000000000000007</v>
+        <v>70.400000000000006</v>
       </c>
       <c r="CE31">
-        <v>12.5</v>
+        <v>19.100000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:83" x14ac:dyDescent="0.3">
@@ -3333,13 +3333,13 @@
         <v>16.089916274817998</v>
       </c>
       <c r="CC32">
-        <v>0.4</v>
+        <v>-0.97</v>
       </c>
       <c r="CD32">
-        <v>0</v>
+        <v>62.1</v>
       </c>
       <c r="CE32">
-        <v>8.3000000000000007</v>
+        <v>16.100000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:83" x14ac:dyDescent="0.3">
@@ -3401,13 +3401,13 @@
         <v>27.2685475444096</v>
       </c>
       <c r="CC33">
-        <v>0.4</v>
+        <v>-0.24</v>
       </c>
       <c r="CD33">
-        <v>0</v>
+        <v>68.900000000000006</v>
       </c>
       <c r="CE33">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="34" spans="1:83" x14ac:dyDescent="0.3">
@@ -3469,13 +3469,13 @@
         <v>33.380092100602198</v>
       </c>
       <c r="CC34">
-        <v>-0.5</v>
+        <v>0.88</v>
       </c>
       <c r="CD34">
-        <v>0</v>
+        <v>43.6</v>
       </c>
       <c r="CE34">
-        <v>12.6</v>
+        <v>20.100000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:83" x14ac:dyDescent="0.3">
@@ -3537,13 +3537,13 @@
         <v>34.006292245974599</v>
       </c>
       <c r="CC35">
-        <v>3.8</v>
+        <v>4.66</v>
       </c>
       <c r="CD35">
-        <v>0.1</v>
+        <v>53</v>
       </c>
       <c r="CE35">
-        <v>7.6</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="36" spans="1:83" x14ac:dyDescent="0.3">
@@ -3605,13 +3605,13 @@
         <v>50.776530894984802</v>
       </c>
       <c r="CC36">
-        <v>2.4</v>
+        <v>6.41</v>
       </c>
       <c r="CD36">
-        <v>0.2</v>
+        <v>81.400000000000006</v>
       </c>
       <c r="CE36">
-        <v>16.600000000000001</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="37" spans="1:83" x14ac:dyDescent="0.3">
@@ -3673,13 +3673,13 @@
         <v>45.933591433388202</v>
       </c>
       <c r="CC37">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
       <c r="CD37">
-        <v>1.1000000000000001</v>
+        <v>114.9</v>
       </c>
       <c r="CE37">
-        <v>17.8</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="38" spans="1:83" x14ac:dyDescent="0.3">
@@ -3741,13 +3741,13 @@
         <v>51.541578862052198</v>
       </c>
       <c r="CC38">
-        <v>7.1</v>
+        <v>9.31</v>
       </c>
       <c r="CD38">
-        <v>1.9</v>
+        <v>90.9</v>
       </c>
       <c r="CE38">
-        <v>17.100000000000001</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="39" spans="1:83" x14ac:dyDescent="0.3">
@@ -3809,10 +3809,10 @@
         <v>52.988309377912103</v>
       </c>
       <c r="CC39">
-        <v>9.5</v>
+        <v>7.61</v>
       </c>
       <c r="CD39">
-        <v>5</v>
+        <v>99.4</v>
       </c>
       <c r="CE39">
         <v>25.8</v>
@@ -3877,13 +3877,13 @@
         <v>40.191045386049602</v>
       </c>
       <c r="CC40">
-        <v>3</v>
+        <v>6.68</v>
       </c>
       <c r="CD40">
-        <v>2.8</v>
+        <v>102</v>
       </c>
       <c r="CE40">
-        <v>14.5</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="41" spans="1:83" x14ac:dyDescent="0.3">
@@ -3945,13 +3945,13 @@
         <v>28.990879549984999</v>
       </c>
       <c r="CC41">
-        <v>6.5</v>
+        <v>3.19</v>
       </c>
       <c r="CD41">
-        <v>0</v>
+        <v>94.5</v>
       </c>
       <c r="CE41">
-        <v>11.4</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="42" spans="1:83" x14ac:dyDescent="0.3">
@@ -4013,13 +4013,13 @@
         <v>13.5049545408111</v>
       </c>
       <c r="CC42">
-        <v>-5.6</v>
+        <v>-0.44</v>
       </c>
       <c r="CD42">
-        <v>0</v>
+        <v>72.8</v>
       </c>
       <c r="CE42">
-        <v>5.6</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="43" spans="1:83" x14ac:dyDescent="0.3">
@@ -4081,13 +4081,13 @@
         <v>9.0191054827611499</v>
       </c>
       <c r="CC43">
-        <v>-1.7</v>
+        <v>-1.25</v>
       </c>
       <c r="CD43">
-        <v>6.7</v>
+        <v>64.599999999999994</v>
       </c>
       <c r="CE43">
-        <v>11.4</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="44" spans="1:83" x14ac:dyDescent="0.3">
@@ -4149,13 +4149,13 @@
         <v>21.593680095121002</v>
       </c>
       <c r="CC44">
-        <v>-1.3</v>
+        <v>-1.91</v>
       </c>
       <c r="CD44">
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="CE44">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:83" x14ac:dyDescent="0.3">
@@ -4217,13 +4217,13 @@
         <v>28.122122216321898</v>
       </c>
       <c r="CC45">
-        <v>-0.1</v>
+        <v>-0.42</v>
       </c>
       <c r="CD45">
-        <v>0</v>
+        <v>54.5</v>
       </c>
       <c r="CE45">
-        <v>8.1</v>
+        <v>19.100000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:83" x14ac:dyDescent="0.3">
@@ -4285,13 +4285,13 @@
         <v>33.241350906095597</v>
       </c>
       <c r="CC46">
-        <v>4.8</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="CD46">
-        <v>2</v>
+        <v>66.099999999999994</v>
       </c>
       <c r="CE46">
-        <v>16.5</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="47" spans="1:83" x14ac:dyDescent="0.3">
@@ -4353,10 +4353,10 @@
         <v>33.752338822198098</v>
       </c>
       <c r="CC47">
-        <v>3.8</v>
+        <v>2.64</v>
       </c>
       <c r="CD47">
-        <v>2.7</v>
+        <v>67.8</v>
       </c>
       <c r="CE47">
         <v>25.5</v>
@@ -4421,13 +4421,13 @@
         <v>54.884541159246702</v>
       </c>
       <c r="CC48">
-        <v>2.5</v>
+        <v>4.13</v>
       </c>
       <c r="CD48">
-        <v>12.7</v>
+        <v>76.3</v>
       </c>
       <c r="CE48">
-        <v>12.6</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="49" spans="1:83" x14ac:dyDescent="0.3">
@@ -4489,10 +4489,10 @@
         <v>44.072258064516099</v>
       </c>
       <c r="CC49">
-        <v>8.4</v>
+        <v>7.78</v>
       </c>
       <c r="CD49">
-        <v>2.4</v>
+        <v>82.4</v>
       </c>
       <c r="CE49">
         <v>29.8</v>
@@ -4584,13 +4584,13 @@
         <v>166873</v>
       </c>
       <c r="CC50">
-        <v>8.5</v>
+        <v>9.61</v>
       </c>
       <c r="CD50">
-        <v>2.7</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="CE50">
-        <v>16.100000000000001</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="51" spans="1:83" x14ac:dyDescent="0.3">
@@ -4679,10 +4679,10 @@
         <v>152047</v>
       </c>
       <c r="CC51">
-        <v>6.3</v>
+        <v>9.6300000000000008</v>
       </c>
       <c r="CD51">
-        <v>3.1</v>
+        <v>66.599999999999994</v>
       </c>
       <c r="CE51">
         <v>25.3</v>
@@ -4774,13 +4774,13 @@
         <v>164428</v>
       </c>
       <c r="CC52">
-        <v>8.8000000000000007</v>
+        <v>8.19</v>
       </c>
       <c r="CD52">
-        <v>0.4</v>
+        <v>80.5</v>
       </c>
       <c r="CE52">
-        <v>21.2</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="53" spans="1:83" x14ac:dyDescent="0.3">
@@ -4869,13 +4869,13 @@
         <v>147980</v>
       </c>
       <c r="CC53">
-        <v>9.1999999999999993</v>
+        <v>2.99</v>
       </c>
       <c r="CD53">
-        <v>0.6</v>
+        <v>91.8</v>
       </c>
       <c r="CE53">
-        <v>18</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="54" spans="1:83" x14ac:dyDescent="0.3">
@@ -4964,13 +4964,13 @@
         <v>134051</v>
       </c>
       <c r="CC54">
-        <v>3.1</v>
+        <v>0.16</v>
       </c>
       <c r="CD54">
-        <v>0.7</v>
+        <v>61.9</v>
       </c>
       <c r="CE54">
-        <v>10.5</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="55" spans="1:83" x14ac:dyDescent="0.3">
@@ -5059,13 +5059,13 @@
         <v>134476</v>
       </c>
       <c r="CC55">
-        <v>-2.2999999999999998</v>
+        <v>-0.82</v>
       </c>
       <c r="CD55">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="CE55">
-        <v>6.9</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="56" spans="1:83" x14ac:dyDescent="0.3">
@@ -5154,13 +5154,13 @@
         <v>154137</v>
       </c>
       <c r="CC56">
-        <v>0</v>
+        <v>-1.76</v>
       </c>
       <c r="CD56">
-        <v>0</v>
+        <v>52.1</v>
       </c>
       <c r="CE56">
-        <v>8.8000000000000007</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:83" x14ac:dyDescent="0.3">
@@ -5249,13 +5249,13 @@
         <v>155496</v>
       </c>
       <c r="CC57">
-        <v>-2.5</v>
+        <v>-1.83</v>
       </c>
       <c r="CD57">
-        <v>0</v>
+        <v>71.599999999999994</v>
       </c>
       <c r="CE57">
-        <v>10.4</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="58" spans="1:83" x14ac:dyDescent="0.3">
@@ -5344,13 +5344,13 @@
         <v>153048</v>
       </c>
       <c r="CC58">
-        <v>-1.4</v>
+        <v>2.37</v>
       </c>
       <c r="CD58">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="CE58">
-        <v>8</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="59" spans="1:83" x14ac:dyDescent="0.3">
@@ -5439,13 +5439,13 @@
         <v>160177</v>
       </c>
       <c r="CC59">
-        <v>4.8</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="CD59">
-        <v>3.3</v>
+        <v>57.5</v>
       </c>
       <c r="CE59">
-        <v>17.8</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="60" spans="1:83" x14ac:dyDescent="0.3">
@@ -5534,13 +5534,13 @@
         <v>157710</v>
       </c>
       <c r="CC60">
-        <v>3.6</v>
+        <v>6.31</v>
       </c>
       <c r="CD60">
-        <v>4.3</v>
+        <v>71.3</v>
       </c>
       <c r="CE60">
-        <v>24.1</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="61" spans="1:83" x14ac:dyDescent="0.3">
@@ -5629,13 +5629,13 @@
         <v>162382</v>
       </c>
       <c r="CC61">
-        <v>8.9</v>
+        <v>8.75</v>
       </c>
       <c r="CD61">
-        <v>1.4</v>
+        <v>113.2</v>
       </c>
       <c r="CE61">
-        <v>17.899999999999999</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="62" spans="1:83" x14ac:dyDescent="0.3">
@@ -5724,13 +5724,13 @@
         <v>161622</v>
       </c>
       <c r="CC62">
-        <v>8.1999999999999993</v>
+        <v>9.31</v>
       </c>
       <c r="CD62">
-        <v>4.5</v>
+        <v>93.7</v>
       </c>
       <c r="CE62">
-        <v>16.399999999999999</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63" spans="1:83" x14ac:dyDescent="0.3">
@@ -5819,13 +5819,13 @@
         <v>143260</v>
       </c>
       <c r="CC63">
-        <v>6.9</v>
+        <v>8.27</v>
       </c>
       <c r="CD63">
-        <v>0.8</v>
+        <v>73.3</v>
       </c>
       <c r="CE63">
-        <v>15.5</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="64" spans="1:83" x14ac:dyDescent="0.3">
@@ -5914,13 +5914,13 @@
         <v>156209</v>
       </c>
       <c r="CC64">
-        <v>4.4000000000000004</v>
+        <v>7.04</v>
       </c>
       <c r="CD64">
-        <v>2.1</v>
+        <v>96.2</v>
       </c>
       <c r="CE64">
-        <v>15.5</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="65" spans="1:83" x14ac:dyDescent="0.3">
@@ -6009,13 +6009,13 @@
         <v>148650</v>
       </c>
       <c r="CC65">
-        <v>4.5</v>
+        <v>3.72</v>
       </c>
       <c r="CD65">
-        <v>0.3</v>
+        <v>92.2</v>
       </c>
       <c r="CE65">
-        <v>9.4</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="66" spans="1:83" x14ac:dyDescent="0.3">
@@ -6104,13 +6104,13 @@
         <v>142060</v>
       </c>
       <c r="CC66">
-        <v>4.5</v>
+        <v>0.13</v>
       </c>
       <c r="CD66">
-        <v>8.6</v>
+        <v>56.6</v>
       </c>
       <c r="CE66">
-        <v>11.3</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="67" spans="1:83" x14ac:dyDescent="0.3">
@@ -6199,13 +6199,13 @@
         <v>152622</v>
       </c>
       <c r="CC67">
-        <v>0.4</v>
+        <v>-0.59</v>
       </c>
       <c r="CD67">
-        <v>1.7</v>
+        <v>98.3</v>
       </c>
       <c r="CE67">
-        <v>9.4</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="68" spans="1:83" x14ac:dyDescent="0.3">
@@ -6294,13 +6294,13 @@
         <v>168082</v>
       </c>
       <c r="CC68">
-        <v>1.1000000000000001</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="CD68">
-        <v>0</v>
+        <v>63.1</v>
       </c>
       <c r="CE68">
-        <v>6.3</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="69" spans="1:83" x14ac:dyDescent="0.3">
@@ -6389,13 +6389,13 @@
         <v>164975</v>
       </c>
       <c r="CC69">
-        <v>0.3</v>
+        <v>-1.08</v>
       </c>
       <c r="CD69">
-        <v>1.1000000000000001</v>
+        <v>84</v>
       </c>
       <c r="CE69">
-        <v>8.3000000000000007</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="70" spans="1:83" x14ac:dyDescent="0.3">
@@ -6484,13 +6484,13 @@
         <v>158580</v>
       </c>
       <c r="CC70">
-        <v>-1.9</v>
+        <v>0.92</v>
       </c>
       <c r="CD70">
-        <v>0.9</v>
+        <v>55.1</v>
       </c>
       <c r="CE70">
-        <v>13.2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71" spans="1:83" x14ac:dyDescent="0.3">
@@ -6579,13 +6579,13 @@
         <v>161389</v>
       </c>
       <c r="CC71">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="CD71">
-        <v>0.1</v>
+        <v>60.3</v>
       </c>
       <c r="CE71">
-        <v>18.899999999999999</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="72" spans="1:83" x14ac:dyDescent="0.3">
@@ -6674,13 +6674,13 @@
         <v>161070</v>
       </c>
       <c r="CC72">
-        <v>2.2000000000000002</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="CD72">
-        <v>0</v>
+        <v>50.9</v>
       </c>
       <c r="CE72">
-        <v>16.8</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="73" spans="1:83" x14ac:dyDescent="0.3">
@@ -6769,13 +6769,13 @@
         <v>163990</v>
       </c>
       <c r="CC73">
-        <v>2.1</v>
+        <v>7.14</v>
       </c>
       <c r="CD73">
-        <v>2.8</v>
+        <v>68</v>
       </c>
       <c r="CE73">
-        <v>17.3</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="74" spans="1:83" x14ac:dyDescent="0.3">
@@ -6864,13 +6864,13 @@
         <v>168113</v>
       </c>
       <c r="CC74">
-        <v>8.4</v>
+        <v>8.25</v>
       </c>
       <c r="CD74">
-        <v>3.8</v>
+        <v>161.80000000000001</v>
       </c>
       <c r="CE74">
-        <v>6.5</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="75" spans="1:83" x14ac:dyDescent="0.3">
@@ -6959,13 +6959,13 @@
         <v>153356</v>
       </c>
       <c r="CC75">
-        <v>7.1</v>
+        <v>7.11</v>
       </c>
       <c r="CD75">
-        <v>1.9</v>
+        <v>96.7</v>
       </c>
       <c r="CE75">
-        <v>15.9</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="76" spans="1:83" x14ac:dyDescent="0.3">
@@ -7054,13 +7054,13 @@
         <v>168671</v>
       </c>
       <c r="CC76">
-        <v>7</v>
+        <v>6.59</v>
       </c>
       <c r="CD76">
-        <v>0.4</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="CE76">
-        <v>13.3</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="77" spans="1:83" x14ac:dyDescent="0.3">
@@ -7149,13 +7149,13 @@
         <v>158088</v>
       </c>
       <c r="CC77">
-        <v>5.4</v>
+        <v>4.63</v>
       </c>
       <c r="CD77">
-        <v>4.5999999999999996</v>
+        <v>52</v>
       </c>
       <c r="CE77">
-        <v>7</v>
+        <v>20.399999999999999</v>
       </c>
     </row>
     <row r="78" spans="1:83" x14ac:dyDescent="0.3">
@@ -7244,13 +7244,13 @@
         <v>141818</v>
       </c>
       <c r="CC78">
-        <v>3</v>
+        <v>1.44</v>
       </c>
       <c r="CD78">
-        <v>6.6</v>
+        <v>63.3</v>
       </c>
       <c r="CE78">
-        <v>17.5</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="79" spans="1:83" x14ac:dyDescent="0.3">
@@ -7339,13 +7339,13 @@
         <v>147480</v>
       </c>
       <c r="CC79">
-        <v>1.1000000000000001</v>
+        <v>-1.89</v>
       </c>
       <c r="CD79">
-        <v>2.5</v>
+        <v>68.8</v>
       </c>
       <c r="CE79">
-        <v>9.8000000000000007</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="80" spans="1:83" x14ac:dyDescent="0.3">
@@ -7434,13 +7434,13 @@
         <v>157356</v>
       </c>
       <c r="CC80">
-        <v>-1.2</v>
+        <v>-1.71</v>
       </c>
       <c r="CD80">
-        <v>3.8</v>
+        <v>45.3</v>
       </c>
       <c r="CE80">
-        <v>9.3000000000000007</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="81" spans="1:83" x14ac:dyDescent="0.3">
@@ -7529,13 +7529,13 @@
         <v>156178</v>
       </c>
       <c r="CC81">
-        <v>-3.5</v>
+        <v>-0.76</v>
       </c>
       <c r="CD81">
-        <v>0</v>
+        <v>30.9</v>
       </c>
       <c r="CE81">
-        <v>6.7</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="82" spans="1:83" x14ac:dyDescent="0.3">
@@ -7624,13 +7624,13 @@
         <v>151500</v>
       </c>
       <c r="CC82">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="CD82">
-        <v>2.4</v>
+        <v>43</v>
       </c>
       <c r="CE82">
-        <v>11.5</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="83" spans="1:83" x14ac:dyDescent="0.3">
@@ -7719,13 +7719,13 @@
         <v>166532</v>
       </c>
       <c r="CC83">
-        <v>1.7</v>
+        <v>3.55</v>
       </c>
       <c r="CD83">
-        <v>1.2</v>
+        <v>43.4</v>
       </c>
       <c r="CE83">
-        <v>8.8000000000000007</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="84" spans="1:83" x14ac:dyDescent="0.3">
@@ -7814,13 +7814,13 @@
         <v>161070</v>
       </c>
       <c r="CC84">
-        <v>7.3</v>
+        <v>6.41</v>
       </c>
       <c r="CD84">
-        <v>0.4</v>
+        <v>58.8</v>
       </c>
       <c r="CE84">
-        <v>7.1</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="85" spans="1:83" x14ac:dyDescent="0.3">
@@ -7909,13 +7909,13 @@
         <v>171027</v>
       </c>
       <c r="CC85">
-        <v>3.2</v>
+        <v>6.17</v>
       </c>
       <c r="CD85">
-        <v>2.5</v>
+        <v>96.2</v>
       </c>
       <c r="CE85">
-        <v>25.4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="86" spans="1:83" x14ac:dyDescent="0.3">
@@ -8004,13 +8004,13 @@
         <v>163866</v>
       </c>
       <c r="CC86">
-        <v>9.5</v>
+        <v>8.43</v>
       </c>
       <c r="CD86">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="CE86">
-        <v>14.8</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="87" spans="1:83" x14ac:dyDescent="0.3">
@@ -8099,13 +8099,13 @@
         <v>148232</v>
       </c>
       <c r="CC87">
-        <v>8.1</v>
+        <v>9.67</v>
       </c>
       <c r="CD87">
-        <v>1.5</v>
+        <v>48.8</v>
       </c>
       <c r="CE87">
-        <v>22.5</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="88" spans="1:83" x14ac:dyDescent="0.3">
@@ -8194,13 +8194,13 @@
         <v>159592</v>
       </c>
       <c r="CC88">
-        <v>11.3</v>
+        <v>7.18</v>
       </c>
       <c r="CD88">
-        <v>0.8</v>
+        <v>52</v>
       </c>
       <c r="CE88">
-        <v>16.3</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="89" spans="1:83" x14ac:dyDescent="0.3">
@@ -8289,13 +8289,13 @@
         <v>145716</v>
       </c>
       <c r="CC89">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="CD89">
-        <v>0.1</v>
+        <v>75.599999999999994</v>
       </c>
       <c r="CE89">
-        <v>10.1</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="90" spans="1:83" x14ac:dyDescent="0.3">
@@ -8384,13 +8384,13 @@
         <v>143347</v>
       </c>
       <c r="CC90">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="CD90">
-        <v>3.6</v>
+        <v>80.5</v>
       </c>
       <c r="CE90">
-        <v>19.7</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="91" spans="1:83" x14ac:dyDescent="0.3">
@@ -8479,13 +8479,13 @@
         <v>145920</v>
       </c>
       <c r="CC91">
-        <v>-1.3</v>
+        <v>-1.55</v>
       </c>
       <c r="CD91">
-        <v>0.3</v>
+        <v>46.5</v>
       </c>
       <c r="CE91">
-        <v>15.1</v>
+        <v>18.399999999999999</v>
       </c>
     </row>
     <row r="92" spans="1:83" x14ac:dyDescent="0.3">
@@ -8574,10 +8574,10 @@
         <v>157976</v>
       </c>
       <c r="CC92">
-        <v>-2.5</v>
+        <v>-1.79</v>
       </c>
       <c r="CD92">
-        <v>2.2999999999999998</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="CE92">
         <v>19.3</v>
@@ -8669,13 +8669,13 @@
         <v>154566</v>
       </c>
       <c r="CC93">
-        <v>0.8</v>
+        <v>-1.36</v>
       </c>
       <c r="CD93">
-        <v>1.3</v>
+        <v>39.5</v>
       </c>
       <c r="CE93">
-        <v>7</v>
+        <v>17.399999999999999</v>
       </c>
     </row>
     <row r="94" spans="1:83" x14ac:dyDescent="0.3">
@@ -8764,13 +8764,13 @@
         <v>146160</v>
       </c>
       <c r="CC94">
-        <v>1.7</v>
+        <v>0.51</v>
       </c>
       <c r="CD94">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="CE94">
-        <v>10.1</v>
+        <v>18.600000000000001</v>
       </c>
     </row>
     <row r="95" spans="1:83" x14ac:dyDescent="0.3">
@@ -8859,13 +8859,13 @@
         <v>157115</v>
       </c>
       <c r="CC95">
-        <v>-0.1</v>
+        <v>3.08</v>
       </c>
       <c r="CD95">
-        <v>0</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="CE95">
-        <v>7.2</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="96" spans="1:83" x14ac:dyDescent="0.3">
@@ -8954,13 +8954,13 @@
         <v>154890</v>
       </c>
       <c r="CC96">
-        <v>7.1</v>
+        <v>6.49</v>
       </c>
       <c r="CD96">
-        <v>0</v>
+        <v>67.099999999999994</v>
       </c>
       <c r="CE96">
-        <v>10.5</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="97" spans="1:83" x14ac:dyDescent="0.3">
@@ -9049,13 +9049,13 @@
         <v>159588</v>
       </c>
       <c r="CC97">
-        <v>7</v>
+        <v>9.69</v>
       </c>
       <c r="CD97">
-        <v>0</v>
+        <v>60.9</v>
       </c>
       <c r="CE97">
-        <v>13.1</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="98" spans="1:83" x14ac:dyDescent="0.3">
@@ -9144,13 +9144,13 @@
         <v>159526</v>
       </c>
       <c r="CC98">
-        <v>8.5</v>
+        <v>9.6199999999999992</v>
       </c>
       <c r="CD98">
-        <v>0.9</v>
+        <v>62.1</v>
       </c>
       <c r="CE98">
-        <v>21.5</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="99" spans="1:83" x14ac:dyDescent="0.3">
@@ -9239,13 +9239,13 @@
         <v>150568</v>
       </c>
       <c r="CC99">
-        <v>5.7</v>
+        <v>6.11</v>
       </c>
       <c r="CD99">
-        <v>4.5</v>
+        <v>76.599999999999994</v>
       </c>
       <c r="CE99">
-        <v>20.3</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="100" spans="1:83" x14ac:dyDescent="0.3">
@@ -9334,13 +9334,13 @@
         <v>159526</v>
       </c>
       <c r="CC100">
-        <v>9.9</v>
+        <v>7.13</v>
       </c>
       <c r="CD100">
-        <v>0</v>
+        <v>90.1</v>
       </c>
       <c r="CE100">
-        <v>17.399999999999999</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="101" spans="1:83" x14ac:dyDescent="0.3">
@@ -9429,13 +9429,13 @@
         <v>150270</v>
       </c>
       <c r="CC101">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="CD101">
-        <v>0.7</v>
+        <v>92.7</v>
       </c>
       <c r="CE101">
-        <v>15.3</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="102" spans="1:83" x14ac:dyDescent="0.3">
@@ -9524,13 +9524,13 @@
         <v>128057</v>
       </c>
       <c r="CC102">
-        <v>0.9</v>
+        <v>-0.26</v>
       </c>
       <c r="CD102">
-        <v>0.4</v>
+        <v>39.4</v>
       </c>
       <c r="CE102">
-        <v>13.7</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="103" spans="1:83" x14ac:dyDescent="0.3">
@@ -9619,13 +9619,13 @@
         <v>136540</v>
       </c>
       <c r="CC103">
-        <v>-3.1</v>
+        <v>-2.82</v>
       </c>
       <c r="CD103">
-        <v>0</v>
+        <v>67.3</v>
       </c>
       <c r="CE103">
-        <v>6.6</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="104" spans="1:83" x14ac:dyDescent="0.3">
@@ -9714,13 +9714,13 @@
         <v>154597</v>
       </c>
       <c r="CC104">
-        <v>-4.7</v>
+        <v>-2.36</v>
       </c>
       <c r="CD104">
-        <v>0</v>
+        <v>57.4</v>
       </c>
       <c r="CE104">
-        <v>13.7</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="105" spans="1:83" x14ac:dyDescent="0.3">
@@ -9809,13 +9809,13 @@
         <v>154721</v>
       </c>
       <c r="CC105">
-        <v>-1.7</v>
+        <v>-0.37</v>
       </c>
       <c r="CD105">
-        <v>0</v>
+        <v>39.5</v>
       </c>
       <c r="CE105">
-        <v>9.4</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="106" spans="1:83" x14ac:dyDescent="0.3">
@@ -9904,13 +9904,13 @@
         <v>146040</v>
       </c>
       <c r="CC106">
-        <v>1.2</v>
+        <v>1.84</v>
       </c>
       <c r="CD106">
-        <v>0.2</v>
+        <v>84.8</v>
       </c>
       <c r="CE106">
-        <v>9.5</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="107" spans="1:83" x14ac:dyDescent="0.3">
@@ -9999,13 +9999,13 @@
         <v>149203</v>
       </c>
       <c r="CC107">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="CD107">
-        <v>0</v>
+        <v>58.6</v>
       </c>
       <c r="CE107">
-        <v>10.7</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="108" spans="1:83" x14ac:dyDescent="0.3">
@@ -10094,13 +10094,13 @@
         <v>146220</v>
       </c>
       <c r="CC108">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="CD108">
-        <v>0.6</v>
+        <v>69</v>
       </c>
       <c r="CE108">
-        <v>10.7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="109" spans="1:83" x14ac:dyDescent="0.3">
@@ -10189,13 +10189,13 @@
         <v>149978</v>
       </c>
       <c r="CC109">
-        <v>9.9</v>
+        <v>6.4</v>
       </c>
       <c r="CD109">
-        <v>5.9</v>
+        <v>126.3</v>
       </c>
       <c r="CE109">
-        <v>13.7</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="110" spans="1:83" x14ac:dyDescent="0.3">
@@ -10284,13 +10284,13 @@
         <v>156333</v>
       </c>
       <c r="CC110">
-        <v>9</v>
+        <v>10.25</v>
       </c>
       <c r="CD110">
-        <v>0.3</v>
+        <v>77.2</v>
       </c>
       <c r="CE110">
-        <v>14</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="111" spans="1:83" x14ac:dyDescent="0.3">
@@ -10379,13 +10379,13 @@
         <v>139444</v>
       </c>
       <c r="CC111">
-        <v>6.7</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="CD111">
-        <v>4.0999999999999996</v>
+        <v>73.5</v>
       </c>
       <c r="CE111">
-        <v>19.600000000000001</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="112" spans="1:83" x14ac:dyDescent="0.3">
@@ -10474,13 +10474,13 @@
         <v>153216</v>
       </c>
       <c r="CC112">
-        <v>10.1</v>
+        <v>7.91</v>
       </c>
       <c r="CD112">
-        <v>0</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="CE112">
-        <v>9.3000000000000007</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="113" spans="1:83" x14ac:dyDescent="0.3">
@@ -10569,13 +10569,13 @@
         <v>138583</v>
       </c>
       <c r="CC113">
-        <v>9.5</v>
+        <v>6.41</v>
       </c>
       <c r="CD113">
-        <v>0</v>
+        <v>49.6</v>
       </c>
       <c r="CE113">
-        <v>15.8</v>
+        <v>20.100000000000001</v>
       </c>
     </row>
     <row r="114" spans="1:83" x14ac:dyDescent="0.3">
@@ -10664,13 +10664,13 @@
         <v>116900</v>
       </c>
       <c r="CC114">
-        <v>3.5</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="CD114">
-        <v>4.0999999999999996</v>
+        <v>66</v>
       </c>
       <c r="CE114">
-        <v>11.8</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="115" spans="1:83" x14ac:dyDescent="0.3">
@@ -10759,13 +10759,13 @@
         <v>118186</v>
       </c>
       <c r="CC115">
-        <v>-2.7</v>
+        <v>-0.43</v>
       </c>
       <c r="CD115">
-        <v>0.7</v>
+        <v>82.2</v>
       </c>
       <c r="CE115">
-        <v>6.9</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="116" spans="1:83" x14ac:dyDescent="0.3">
@@ -10854,13 +10854,13 @@
         <v>140988</v>
       </c>
       <c r="CC116">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="CD116">
-        <v>6.6</v>
+        <v>83.8</v>
       </c>
       <c r="CE116">
-        <v>20.5</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="117" spans="1:83" x14ac:dyDescent="0.3">
@@ -10949,13 +10949,13 @@
         <v>141360</v>
       </c>
       <c r="CC117">
-        <v>-2.7</v>
+        <v>-1.83</v>
       </c>
       <c r="CD117">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="CE117">
-        <v>13.2</v>
+        <v>18.899999999999999</v>
       </c>
     </row>
     <row r="118" spans="1:83" x14ac:dyDescent="0.3">
@@ -11044,13 +11044,13 @@
         <v>139992</v>
       </c>
       <c r="CC118">
-        <v>-0.6</v>
+        <v>0.94</v>
       </c>
       <c r="CD118">
-        <v>0</v>
+        <v>20.6</v>
       </c>
       <c r="CE118">
-        <v>8.6999999999999993</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="119" spans="1:83" x14ac:dyDescent="0.3">
@@ -11139,13 +11139,13 @@
         <v>146261</v>
       </c>
       <c r="CC119">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="CD119">
-        <v>2.5</v>
+        <v>52.8</v>
       </c>
       <c r="CE119">
-        <v>8.8000000000000007</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="120" spans="1:83" x14ac:dyDescent="0.3">
@@ -11234,13 +11234,13 @@
         <v>142930</v>
       </c>
       <c r="CC120">
-        <v>6</v>
+        <v>4.87</v>
       </c>
       <c r="CD120">
-        <v>1.6</v>
+        <v>76.599999999999994</v>
       </c>
       <c r="CE120">
-        <v>15.4</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="121" spans="1:83" x14ac:dyDescent="0.3">
@@ -11329,13 +11329,13 @@
         <v>149295</v>
       </c>
       <c r="CC121">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
       <c r="CD121">
-        <v>1.2</v>
+        <v>107</v>
       </c>
       <c r="CE121">
-        <v>18.3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="122" spans="1:83" x14ac:dyDescent="0.3">
@@ -11424,13 +11424,13 @@
         <v>141949</v>
       </c>
       <c r="CC122">
-        <v>5.6</v>
+        <v>7.16</v>
       </c>
       <c r="CD122">
-        <v>5</v>
+        <v>97.8</v>
       </c>
       <c r="CE122">
-        <v>16.100000000000001</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="123" spans="1:83" x14ac:dyDescent="0.3">
@@ -11519,13 +11519,13 @@
         <v>124628</v>
       </c>
       <c r="CC123">
-        <v>7.3</v>
+        <v>8.41</v>
       </c>
       <c r="CD123">
-        <v>8.6999999999999993</v>
+        <v>58</v>
       </c>
       <c r="CE123">
-        <v>7.2</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="124" spans="1:83" x14ac:dyDescent="0.3">
@@ -11614,13 +11614,13 @@
         <v>138012</v>
       </c>
       <c r="CC124">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="CD124">
-        <v>3.9</v>
+        <v>171.9</v>
       </c>
       <c r="CE124">
-        <v>14.3</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="125" spans="1:83" x14ac:dyDescent="0.3">
@@ -11709,13 +11709,13 @@
         <v>130474</v>
       </c>
       <c r="CC125">
-        <v>3.2</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="CD125">
-        <v>0</v>
+        <v>50.7</v>
       </c>
       <c r="CE125">
-        <v>10.199999999999999</v>
+        <v>18.600000000000001</v>
       </c>
     </row>
     <row r="126" spans="1:83" x14ac:dyDescent="0.3">
@@ -11804,13 +11804,13 @@
         <v>112071</v>
       </c>
       <c r="CC126">
-        <v>2.4</v>
+        <v>1.08</v>
       </c>
       <c r="CD126">
-        <v>0.5</v>
+        <v>46.5</v>
       </c>
       <c r="CE126">
-        <v>13.8</v>
+        <v>17.899999999999999</v>
       </c>
     </row>
     <row r="127" spans="1:83" x14ac:dyDescent="0.3">
@@ -11899,13 +11899,13 @@
         <v>119551</v>
       </c>
       <c r="CC127">
-        <v>1</v>
+        <v>-0.75</v>
       </c>
       <c r="CD127">
-        <v>6.1</v>
+        <v>51.8</v>
       </c>
       <c r="CE127">
-        <v>8.3000000000000007</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="128" spans="1:83" x14ac:dyDescent="0.3">
@@ -11994,13 +11994,13 @@
         <v>136851</v>
       </c>
       <c r="CC128">
-        <v>-0.6</v>
+        <v>-1.38</v>
       </c>
       <c r="CD128">
-        <v>0</v>
+        <v>47.4</v>
       </c>
       <c r="CE128">
-        <v>13.6</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="129" spans="1:83" x14ac:dyDescent="0.3">
@@ -12089,13 +12089,13 @@
         <v>138787</v>
       </c>
       <c r="CC129">
-        <v>-0.8</v>
+        <v>0.18</v>
       </c>
       <c r="CD129">
-        <v>0.2</v>
+        <v>57.3</v>
       </c>
       <c r="CE129">
-        <v>7.9</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="130" spans="1:83" x14ac:dyDescent="0.3">
@@ -12184,13 +12184,13 @@
         <v>136350</v>
       </c>
       <c r="CC130">
-        <v>2.2000000000000002</v>
+        <v>1.22</v>
       </c>
       <c r="CD130">
-        <v>2.2000000000000002</v>
+        <v>68.3</v>
       </c>
       <c r="CE130">
-        <v>6.1</v>
+        <v>17.899999999999999</v>
       </c>
     </row>
     <row r="131" spans="1:83" x14ac:dyDescent="0.3">
@@ -12279,13 +12279,13 @@
         <v>146360</v>
       </c>
       <c r="CC131">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="CD131">
-        <v>0</v>
+        <v>56.3</v>
       </c>
       <c r="CE131">
-        <v>6.8</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="132" spans="1:83" x14ac:dyDescent="0.3">
@@ -12374,13 +12374,13 @@
         <v>141570</v>
       </c>
       <c r="CC132">
-        <v>2.4</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="CD132">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="CE132">
-        <v>11</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="133" spans="1:83" x14ac:dyDescent="0.3">
@@ -12469,13 +12469,13 @@
         <v>144336</v>
       </c>
       <c r="CC133">
-        <v>7.5</v>
+        <v>7.21</v>
       </c>
       <c r="CD133">
-        <v>7.6</v>
+        <v>120.7</v>
       </c>
       <c r="CE133">
-        <v>15.5</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="134" spans="1:83" x14ac:dyDescent="0.3">
@@ -12573,13 +12573,13 @@
         <v>154969</v>
       </c>
       <c r="CC134">
-        <v>8.9</v>
+        <v>8.5399999999999991</v>
       </c>
       <c r="CD134">
-        <v>0.5</v>
+        <v>45.1</v>
       </c>
       <c r="CE134">
-        <v>10.199999999999999</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="135" spans="1:83" x14ac:dyDescent="0.3">
@@ -12677,13 +12677,13 @@
         <v>139440</v>
       </c>
       <c r="CC135">
-        <v>8.3000000000000007</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="CD135">
-        <v>5.0999999999999996</v>
+        <v>86.6</v>
       </c>
       <c r="CE135">
-        <v>23.3</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="136" spans="1:83" x14ac:dyDescent="0.3">
@@ -12781,13 +12781,13 @@
         <v>153650</v>
       </c>
       <c r="CC136">
-        <v>8.9</v>
+        <v>7.53</v>
       </c>
       <c r="CD136">
-        <v>1.1000000000000001</v>
+        <v>79.099999999999994</v>
       </c>
       <c r="CE136">
-        <v>23.5</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="137" spans="1:83" x14ac:dyDescent="0.3">
@@ -12885,13 +12885,13 @@
         <v>142958</v>
       </c>
       <c r="CC137">
-        <v>3.5</v>
+        <v>3.97</v>
       </c>
       <c r="CD137">
-        <v>8.1</v>
+        <v>57.1</v>
       </c>
       <c r="CE137">
-        <v>20.399999999999999</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="138" spans="1:83" x14ac:dyDescent="0.3">
@@ -12989,13 +12989,13 @@
         <v>124273</v>
       </c>
       <c r="CC138">
-        <v>1.8</v>
+        <v>1.35</v>
       </c>
       <c r="CD138">
-        <v>0.2</v>
+        <v>85.2</v>
       </c>
       <c r="CE138">
-        <v>11.9</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="139" spans="1:83" x14ac:dyDescent="0.3">
@@ -13093,13 +13093,13 @@
         <v>126785</v>
       </c>
       <c r="CC139">
-        <v>-1.2</v>
+        <v>-1.94</v>
       </c>
       <c r="CD139">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="CE139">
-        <v>6</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="140" spans="1:83" x14ac:dyDescent="0.3">
@@ -13197,13 +13197,13 @@
         <v>152000</v>
       </c>
       <c r="CC140">
-        <v>-2.5</v>
+        <v>-2.0099999999999998</v>
       </c>
       <c r="CD140">
-        <v>0.2</v>
+        <v>73.2</v>
       </c>
       <c r="CE140">
-        <v>11.8</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="141" spans="1:83" x14ac:dyDescent="0.3">
@@ -13301,13 +13301,13 @@
         <v>160270</v>
       </c>
       <c r="CC141">
-        <v>-3.9</v>
+        <v>-0.97</v>
       </c>
       <c r="CD141">
-        <v>0</v>
+        <v>58.6</v>
       </c>
       <c r="CE141">
-        <v>7.3</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="142" spans="1:83" x14ac:dyDescent="0.3">
@@ -13405,13 +13405,13 @@
         <v>155148</v>
       </c>
       <c r="CC142">
-        <v>3.5</v>
+        <v>-0.16</v>
       </c>
       <c r="CD142">
-        <v>4.9000000000000004</v>
+        <v>71.099999999999994</v>
       </c>
       <c r="CE142">
-        <v>17.8</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="143" spans="1:83" x14ac:dyDescent="0.3">
@@ -13509,13 +13509,13 @@
         <v>158472</v>
       </c>
       <c r="CC143">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="CD143">
-        <v>0</v>
+        <v>40.4</v>
       </c>
       <c r="CE143">
-        <v>9.6</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="144" spans="1:83" x14ac:dyDescent="0.3">
@@ -13613,13 +13613,13 @@
         <v>152130</v>
       </c>
       <c r="CC144">
-        <v>3.3</v>
+        <v>4.9800000000000004</v>
       </c>
       <c r="CD144">
-        <v>2.4</v>
+        <v>82</v>
       </c>
       <c r="CE144">
-        <v>13.9</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="145" spans="1:83" x14ac:dyDescent="0.3">
@@ -13717,13 +13717,13 @@
         <v>155336</v>
       </c>
       <c r="CC145">
-        <v>7.1</v>
+        <v>7.07</v>
       </c>
       <c r="CD145">
-        <v>0.9</v>
+        <v>51</v>
       </c>
       <c r="CE145">
-        <v>17.899999999999999</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="146" spans="1:83" x14ac:dyDescent="0.3">
@@ -13821,13 +13821,13 @@
         <v>165106</v>
       </c>
       <c r="CC146">
-        <v>12.5</v>
+        <v>8.84</v>
       </c>
       <c r="CD146">
-        <v>0</v>
+        <v>55.2</v>
       </c>
       <c r="CE146">
-        <v>10.199999999999999</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="147" spans="1:83" x14ac:dyDescent="0.3">
@@ -13925,13 +13925,13 @@
         <v>153671</v>
       </c>
       <c r="CC147">
-        <v>11.1</v>
+        <v>8.14</v>
       </c>
       <c r="CD147">
-        <v>3.9</v>
+        <v>85.5</v>
       </c>
       <c r="CE147">
-        <v>17.899999999999999</v>
+        <v>26</v>
       </c>
     </row>
     <row r="148" spans="1:83" x14ac:dyDescent="0.3">
@@ -14029,13 +14029,13 @@
         <v>165633</v>
       </c>
       <c r="CC148">
-        <v>11.1</v>
+        <v>7.98</v>
       </c>
       <c r="CD148">
-        <v>0.5</v>
+        <v>77.099999999999994</v>
       </c>
       <c r="CE148">
-        <v>7.9</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="149" spans="1:83" x14ac:dyDescent="0.3">
@@ -14133,13 +14133,13 @@
         <v>141840</v>
       </c>
       <c r="CC149">
-        <v>4</v>
+        <v>3.08</v>
       </c>
       <c r="CD149">
-        <v>8</v>
+        <v>49.9</v>
       </c>
       <c r="CE149">
-        <v>16.3</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="150" spans="1:83" x14ac:dyDescent="0.3">
@@ -14237,10 +14237,10 @@
         <v>127149</v>
       </c>
       <c r="CC150">
-        <v>2.2999999999999998</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="CD150">
-        <v>0.3</v>
+        <v>17.3</v>
       </c>
       <c r="CE150">
         <v>25</v>
@@ -14341,13 +14341,13 @@
         <v>133950</v>
       </c>
       <c r="CC151">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="CD151">
-        <v>0</v>
+        <v>45.2</v>
       </c>
       <c r="CE151">
-        <v>5</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="152" spans="1:83" x14ac:dyDescent="0.3">
@@ -14445,13 +14445,13 @@
         <v>161975</v>
       </c>
       <c r="CC152">
-        <v>-1.5</v>
+        <v>-0.85</v>
       </c>
       <c r="CD152">
-        <v>0.4</v>
+        <v>57.9</v>
       </c>
       <c r="CE152">
-        <v>13.8</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="153" spans="1:83" x14ac:dyDescent="0.3">
@@ -14549,13 +14549,13 @@
         <v>165912</v>
       </c>
       <c r="CC153">
-        <v>0.4</v>
+        <v>-1.02</v>
       </c>
       <c r="CD153">
-        <v>0</v>
+        <v>65.400000000000006</v>
       </c>
       <c r="CE153">
-        <v>7.6</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="154" spans="1:83" x14ac:dyDescent="0.3">
@@ -14653,13 +14653,13 @@
         <v>156030</v>
       </c>
       <c r="CC154">
-        <v>1.8</v>
+        <v>2.59</v>
       </c>
       <c r="CD154">
-        <v>4.8</v>
+        <v>22.3</v>
       </c>
       <c r="CE154">
-        <v>15.6</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="155" spans="1:83" x14ac:dyDescent="0.3">
@@ -14757,13 +14757,13 @@
         <v>181381</v>
       </c>
       <c r="CC155">
-        <v>4.5999999999999996</v>
+        <v>5.85</v>
       </c>
       <c r="CD155">
-        <v>4.5</v>
+        <v>44.1</v>
       </c>
       <c r="CE155">
-        <v>8.9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="156" spans="1:83" x14ac:dyDescent="0.3">
@@ -14861,13 +14861,13 @@
         <v>162420</v>
       </c>
       <c r="CC156">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="CD156">
-        <v>0.4</v>
+        <v>89.5</v>
       </c>
       <c r="CE156">
-        <v>19.7</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="157" spans="1:83" x14ac:dyDescent="0.3">
@@ -14965,13 +14965,13 @@
         <v>163306</v>
       </c>
       <c r="CC157">
-        <v>7.2</v>
+        <v>7.88</v>
       </c>
       <c r="CD157">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="CE157">
-        <v>9.5</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="158" spans="1:83" x14ac:dyDescent="0.3">
@@ -15069,13 +15069,13 @@
         <v>163525</v>
       </c>
       <c r="CC158">
-        <v>10.5</v>
+        <v>8.52</v>
       </c>
       <c r="CD158">
-        <v>1.8</v>
+        <v>126.2</v>
       </c>
       <c r="CE158">
-        <v>14.2</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="159" spans="1:83" x14ac:dyDescent="0.3">
@@ -15173,13 +15173,13 @@
         <v>147336</v>
       </c>
       <c r="CC159">
-        <v>11.3</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="CD159">
-        <v>0.9</v>
+        <v>112.3</v>
       </c>
       <c r="CE159">
-        <v>23.5</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="160" spans="1:83" x14ac:dyDescent="0.3">
@@ -15277,13 +15277,13 @@
         <v>163277</v>
       </c>
       <c r="CC160">
-        <v>6.9</v>
+        <v>8.01</v>
       </c>
       <c r="CD160">
-        <v>10.4</v>
+        <v>71.599999999999994</v>
       </c>
       <c r="CE160">
-        <v>30.2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="161" spans="1:83" x14ac:dyDescent="0.3">
@@ -15381,13 +15381,13 @@
         <v>141720</v>
       </c>
       <c r="CC161">
-        <v>8.5</v>
+        <v>5.67</v>
       </c>
       <c r="CD161">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="CE161">
-        <v>11.7</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="162" spans="1:83" x14ac:dyDescent="0.3">
@@ -15485,13 +15485,13 @@
         <v>140709</v>
       </c>
       <c r="CC162">
-        <v>8.1999999999999993</v>
+        <v>3.25</v>
       </c>
       <c r="CD162">
-        <v>2.8</v>
+        <v>108</v>
       </c>
       <c r="CE162">
-        <v>11.5</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="163" spans="1:83" x14ac:dyDescent="0.3">
@@ -15589,13 +15589,13 @@
         <v>138570</v>
       </c>
       <c r="CC163">
-        <v>1.3</v>
+        <v>-0.51</v>
       </c>
       <c r="CD163">
-        <v>0</v>
+        <v>80.400000000000006</v>
       </c>
       <c r="CE163">
-        <v>13.3</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="164" spans="1:83" x14ac:dyDescent="0.3">
@@ -15693,13 +15693,13 @@
         <v>146444</v>
       </c>
       <c r="CC164">
-        <v>4.3</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="CD164">
-        <v>3.5</v>
+        <v>70.8</v>
       </c>
       <c r="CE164">
-        <v>26.3</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="165" spans="1:83" x14ac:dyDescent="0.3">
@@ -15797,13 +15797,13 @@
         <v>152706</v>
       </c>
       <c r="CC165">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="CD165">
-        <v>4.5999999999999996</v>
+        <v>126.7</v>
       </c>
       <c r="CE165">
-        <v>20.2</v>
+        <v>40.799999999999997</v>
       </c>
     </row>
     <row r="166" spans="1:83" x14ac:dyDescent="0.3">
@@ -15901,13 +15901,13 @@
         <v>147330</v>
       </c>
       <c r="CC166">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="CD166">
-        <v>0.5</v>
+        <v>96.6</v>
       </c>
       <c r="CE166">
-        <v>13</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="167" spans="1:83" x14ac:dyDescent="0.3">
@@ -16005,13 +16005,13 @@
         <v>156023</v>
       </c>
       <c r="CC167">
-        <v>2</v>
+        <v>4.41</v>
       </c>
       <c r="CD167">
-        <v>0</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="CE167">
-        <v>12.3</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="168" spans="1:83" x14ac:dyDescent="0.3">
@@ -16109,13 +16109,13 @@
         <v>156240</v>
       </c>
       <c r="CC168">
-        <v>6.7</v>
+        <v>6.73</v>
       </c>
       <c r="CD168">
-        <v>0</v>
+        <v>150.4</v>
       </c>
       <c r="CE168">
-        <v>12.8</v>
+        <v>34.799999999999997</v>
       </c>
     </row>
     <row r="169" spans="1:83" x14ac:dyDescent="0.3">
@@ -16213,13 +16213,13 @@
         <v>145321</v>
       </c>
       <c r="CC169">
-        <v>8</v>
+        <v>7.59</v>
       </c>
       <c r="CD169">
-        <v>0.3</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="CE169">
-        <v>22.7</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="170" spans="1:83" x14ac:dyDescent="0.3">
@@ -16317,13 +16317,13 @@
         <v>157573</v>
       </c>
       <c r="CC170">
-        <v>6.5</v>
+        <v>9.57</v>
       </c>
       <c r="CD170">
-        <v>7.2</v>
+        <v>136.80000000000001</v>
       </c>
       <c r="CE170">
-        <v>17.100000000000001</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="171" spans="1:83" x14ac:dyDescent="0.3">
@@ -16421,13 +16421,13 @@
         <v>142660</v>
       </c>
       <c r="CC171">
-        <v>12.2</v>
+        <v>9.89</v>
       </c>
       <c r="CD171">
-        <v>1.3</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="CE171">
-        <v>13.2</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="172" spans="1:83" x14ac:dyDescent="0.3">
@@ -16525,13 +16525,13 @@
         <v>154783</v>
       </c>
       <c r="CC172">
-        <v>8.6</v>
+        <v>6.97</v>
       </c>
       <c r="CD172">
-        <v>5.0999999999999996</v>
+        <v>92.5</v>
       </c>
       <c r="CE172">
-        <v>23.5</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="173" spans="1:83" x14ac:dyDescent="0.3">
@@ -16629,13 +16629,13 @@
         <v>138926</v>
       </c>
       <c r="CC173">
-        <v>8.3000000000000007</v>
+        <v>4.34</v>
       </c>
       <c r="CD173">
-        <v>1.1000000000000001</v>
+        <v>62</v>
       </c>
       <c r="CE173">
-        <v>9.4</v>
+        <v>34.799999999999997</v>
       </c>
     </row>
     <row r="174" spans="1:83" x14ac:dyDescent="0.3">
@@ -16733,13 +16733,13 @@
         <v>117118</v>
       </c>
       <c r="CC174">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="CD174">
-        <v>0</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="CE174">
-        <v>13.4</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="175" spans="1:83" x14ac:dyDescent="0.3">
@@ -16837,13 +16837,13 @@
         <v>129750</v>
       </c>
       <c r="CC175">
-        <v>3.4</v>
+        <v>0.42</v>
       </c>
       <c r="CD175">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="CE175">
-        <v>10.8</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="176" spans="1:83" x14ac:dyDescent="0.3">
@@ -16941,13 +16941,13 @@
         <v>146537</v>
       </c>
       <c r="CC176">
-        <v>-1.3</v>
+        <v>0.44</v>
       </c>
       <c r="CD176">
-        <v>18.899999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="CE176">
-        <v>22.1</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="177" spans="1:83" x14ac:dyDescent="0.3">
@@ -17045,13 +17045,13 @@
         <v>146688</v>
       </c>
       <c r="CC177">
-        <v>2.2999999999999998</v>
+        <v>1.75</v>
       </c>
       <c r="CD177">
-        <v>5.6</v>
+        <v>58.5</v>
       </c>
       <c r="CE177">
-        <v>16.600000000000001</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="178" spans="1:83" x14ac:dyDescent="0.3">
@@ -17149,13 +17149,13 @@
         <v>142095</v>
       </c>
       <c r="CC178">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="CD178">
-        <v>0.5</v>
+        <v>87.7</v>
       </c>
       <c r="CE178">
-        <v>26.6</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="179" spans="1:83" x14ac:dyDescent="0.3">
@@ -17253,13 +17253,13 @@
         <v>150598</v>
       </c>
       <c r="CC179">
-        <v>-1.3</v>
+        <v>3.73</v>
       </c>
       <c r="CD179">
-        <v>0.5</v>
+        <v>78.900000000000006</v>
       </c>
       <c r="CE179">
-        <v>14.6</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="180" spans="1:83" x14ac:dyDescent="0.3">
@@ -17357,13 +17357,13 @@
         <v>148810</v>
       </c>
       <c r="CC180">
-        <v>7</v>
+        <v>6.96</v>
       </c>
       <c r="CD180">
-        <v>1.1000000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="CE180">
-        <v>22.5</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="181" spans="1:83" x14ac:dyDescent="0.3">
@@ -17461,13 +17461,13 @@
         <v>152764</v>
       </c>
       <c r="CC181">
-        <v>8.5</v>
+        <v>8.65</v>
       </c>
       <c r="CD181">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="CE181">
-        <v>20.7</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="182" spans="1:83" x14ac:dyDescent="0.3">
@@ -17565,13 +17565,13 @@
         <v>157939</v>
       </c>
       <c r="CC182">
-        <v>5.2</v>
+        <v>7.92</v>
       </c>
       <c r="CD182">
-        <v>2.2999999999999998</v>
+        <v>96.7</v>
       </c>
       <c r="CE182">
-        <v>23.4</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="183" spans="1:83" x14ac:dyDescent="0.3">
@@ -17669,13 +17669,13 @@
         <v>142513</v>
       </c>
       <c r="CC183">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="CD183">
-        <v>3</v>
+        <v>114.3</v>
       </c>
       <c r="CE183">
-        <v>18.600000000000001</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="184" spans="1:83" x14ac:dyDescent="0.3">
@@ -17773,13 +17773,13 @@
         <v>150062</v>
       </c>
       <c r="CC184">
-        <v>7.9</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="CD184">
-        <v>0.5</v>
+        <v>108.2</v>
       </c>
       <c r="CE184">
-        <v>13</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="185" spans="1:83" x14ac:dyDescent="0.3">
@@ -17877,13 +17877,13 @@
         <v>134898</v>
       </c>
       <c r="CC185">
-        <v>9.6</v>
+        <v>4.66</v>
       </c>
       <c r="CD185">
-        <v>3.8</v>
+        <v>128.19999999999999</v>
       </c>
       <c r="CE185">
-        <v>14.9</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="186" spans="1:83" x14ac:dyDescent="0.3">
@@ -17981,13 +17981,13 @@
         <v>118111</v>
       </c>
       <c r="CC186">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="CD186">
-        <v>2.9</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="CE186">
-        <v>17.5</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="187" spans="1:83" x14ac:dyDescent="0.3">
@@ -18085,13 +18085,13 @@
         <v>115872</v>
       </c>
       <c r="CC187">
-        <v>1.2</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="CD187">
-        <v>2.2999999999999998</v>
+        <v>88.2</v>
       </c>
       <c r="CE187">
-        <v>16.3</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="188" spans="1:83" x14ac:dyDescent="0.3">
@@ -18189,13 +18189,13 @@
         <v>137272</v>
       </c>
       <c r="CC188">
-        <v>0.3</v>
+        <v>0.77</v>
       </c>
       <c r="CD188">
-        <v>2.5</v>
+        <v>54.6</v>
       </c>
       <c r="CE188">
-        <v>13.3</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="189" spans="1:83" x14ac:dyDescent="0.3">
@@ -18293,13 +18293,13 @@
         <v>138560</v>
       </c>
       <c r="CC189">
-        <v>2.2000000000000002</v>
+        <v>1.05</v>
       </c>
       <c r="CD189">
-        <v>0.5</v>
+        <v>87.5</v>
       </c>
       <c r="CE189">
-        <v>10.9</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="190" spans="1:83" x14ac:dyDescent="0.3">
@@ -18397,13 +18397,13 @@
         <v>137154</v>
       </c>
       <c r="CC190">
-        <v>0</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="CD190">
-        <v>20.9</v>
+        <v>122.8</v>
       </c>
       <c r="CE190">
-        <v>24.7</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="191" spans="1:83" x14ac:dyDescent="0.3">
@@ -18501,13 +18501,13 @@
         <v>146365</v>
       </c>
       <c r="CC191">
-        <v>1.5</v>
+        <v>4.45</v>
       </c>
       <c r="CD191">
-        <v>5.6</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="CE191">
-        <v>16.600000000000001</v>
+        <v>37.799999999999997</v>
       </c>
     </row>
     <row r="192" spans="1:83" x14ac:dyDescent="0.3">
@@ -18605,13 +18605,13 @@
         <v>144270</v>
       </c>
       <c r="CC192">
-        <v>4.8</v>
+        <v>6.74</v>
       </c>
       <c r="CD192">
-        <v>3.1</v>
+        <v>85.9</v>
       </c>
       <c r="CE192">
-        <v>22.4</v>
+        <v>39.299999999999997</v>
       </c>
     </row>
     <row r="193" spans="1:83" x14ac:dyDescent="0.3">
@@ -18709,13 +18709,13 @@
         <v>145328</v>
       </c>
       <c r="CC193">
-        <v>9.4</v>
+        <v>8.75</v>
       </c>
       <c r="CD193">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="CE193">
-        <v>7.7</v>
+        <v>40.200000000000003</v>
       </c>
     </row>
     <row r="194" spans="1:83" x14ac:dyDescent="0.3">
@@ -18813,13 +18813,13 @@
         <v>151435</v>
       </c>
       <c r="CC194">
-        <v>14.2</v>
+        <v>9.39</v>
       </c>
       <c r="CD194">
-        <v>0.6</v>
+        <v>175</v>
       </c>
       <c r="CE194">
-        <v>22.5</v>
+        <v>32.700000000000003</v>
       </c>
     </row>
     <row r="195" spans="1:83" x14ac:dyDescent="0.3">
@@ -18917,13 +18917,13 @@
         <v>150974</v>
       </c>
       <c r="CC195">
-        <v>11.1</v>
+        <v>10.14</v>
       </c>
       <c r="CD195">
-        <v>4.7</v>
+        <v>125.8</v>
       </c>
       <c r="CE195">
-        <v>17.600000000000001</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="196" spans="1:83" x14ac:dyDescent="0.3">
@@ -19021,13 +19021,13 @@
         <v>98306</v>
       </c>
       <c r="CC196">
-        <v>11.7</v>
+        <v>8.82</v>
       </c>
       <c r="CD196">
-        <v>8</v>
+        <v>127.2</v>
       </c>
       <c r="CE196">
-        <v>14.6</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="197" spans="1:83" x14ac:dyDescent="0.3">
@@ -19080,13 +19080,13 @@
         <v>0</v>
       </c>
       <c r="CC197">
-        <v>9.6999999999999993</v>
+        <v>6.59</v>
       </c>
       <c r="CD197">
-        <v>0</v>
+        <v>62.7</v>
       </c>
       <c r="CE197">
-        <v>19.8</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="198" spans="1:83" x14ac:dyDescent="0.3">
@@ -19139,13 +19139,13 @@
         <v>0</v>
       </c>
       <c r="CC198">
-        <v>5.0999999999999996</v>
+        <v>4.22</v>
       </c>
       <c r="CD198">
-        <v>0</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="CE198">
-        <v>15</v>
+        <v>36.700000000000003</v>
       </c>
     </row>
     <row r="199" spans="1:83" x14ac:dyDescent="0.3">
@@ -19216,13 +19216,13 @@
         <v>2.6</v>
       </c>
       <c r="CC199">
-        <v>4.5</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="CD199">
-        <v>6</v>
+        <v>82.3</v>
       </c>
       <c r="CE199">
-        <v>15.5</v>
+        <v>34.700000000000003</v>
       </c>
     </row>
     <row r="200" spans="1:83" x14ac:dyDescent="0.3">
@@ -19293,13 +19293,13 @@
         <v>1.9</v>
       </c>
       <c r="CC200">
-        <v>-2.5</v>
+        <v>-1.27</v>
       </c>
       <c r="CD200">
-        <v>0</v>
+        <v>46.6</v>
       </c>
       <c r="CE200">
-        <v>7.2</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="201" spans="1:83" x14ac:dyDescent="0.3">
@@ -19367,13 +19367,13 @@
         <v>207</v>
       </c>
       <c r="CC201">
-        <v>3.5</v>
+        <v>0.12</v>
       </c>
       <c r="CD201">
-        <v>8.6</v>
+        <v>115.2</v>
       </c>
       <c r="CE201">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="202" spans="1:83" x14ac:dyDescent="0.3">
@@ -19444,13 +19444,13 @@
         <v>6.4</v>
       </c>
       <c r="CC202">
-        <v>1.5</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="CD202">
-        <v>0</v>
+        <v>101.7</v>
       </c>
       <c r="CE202">
-        <v>9.1</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="203" spans="1:83" x14ac:dyDescent="0.3">
@@ -19521,13 +19521,13 @@
         <v>2.9</v>
       </c>
       <c r="CC203">
-        <v>-2.5</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="CD203">
-        <v>15.7</v>
+        <v>100.3</v>
       </c>
       <c r="CE203">
-        <v>26.7</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="204" spans="1:83" x14ac:dyDescent="0.3">
@@ -19625,13 +19625,13 @@
         <v>35326</v>
       </c>
       <c r="CC204">
-        <v>9.6999999999999993</v>
+        <v>8.34</v>
       </c>
       <c r="CD204">
-        <v>1.1000000000000001</v>
+        <v>64</v>
       </c>
       <c r="CE204">
-        <v>19</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="205" spans="1:83" x14ac:dyDescent="0.3">
@@ -19729,13 +19729,13 @@
         <v>66997</v>
       </c>
       <c r="CC205">
-        <v>5.7</v>
+        <v>8.41</v>
       </c>
       <c r="CD205">
-        <v>2.2999999999999998</v>
+        <v>115.4</v>
       </c>
       <c r="CE205">
-        <v>21.1</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="206" spans="1:83" x14ac:dyDescent="0.3">
@@ -19833,13 +19833,13 @@
         <v>108463</v>
       </c>
       <c r="CC206">
-        <v>13.7</v>
+        <v>9.25</v>
       </c>
       <c r="CD206">
-        <v>1.6</v>
+        <v>76.599999999999994</v>
       </c>
       <c r="CE206">
-        <v>24.7</v>
+        <v>33.299999999999997</v>
       </c>
     </row>
     <row r="207" spans="1:83" x14ac:dyDescent="0.3">
@@ -19937,13 +19937,13 @@
         <v>101726</v>
       </c>
       <c r="CC207">
-        <v>9.6</v>
+        <v>10.14</v>
       </c>
       <c r="CD207">
-        <v>9.1</v>
+        <v>97</v>
       </c>
       <c r="CE207">
-        <v>23</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="208" spans="1:83" x14ac:dyDescent="0.3">
@@ -20041,13 +20041,13 @@
         <v>106392</v>
       </c>
       <c r="CC208">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
       <c r="CD208">
-        <v>0.3</v>
+        <v>99.9</v>
       </c>
       <c r="CE208">
-        <v>10.5</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
     <row r="209" spans="1:83" x14ac:dyDescent="0.3">
@@ -20145,13 +20145,13 @@
         <v>109302</v>
       </c>
       <c r="CC209">
-        <v>6.3</v>
+        <v>5.94</v>
       </c>
       <c r="CD209">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="CE209">
-        <v>20</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="210" spans="1:83" x14ac:dyDescent="0.3">
@@ -20249,13 +20249,13 @@
         <v>89096</v>
       </c>
       <c r="CC210">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="CD210">
-        <v>1.5</v>
+        <v>85.3</v>
       </c>
       <c r="CE210">
-        <v>8.1999999999999993</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="211" spans="1:83" x14ac:dyDescent="0.3">
@@ -20353,13 +20353,13 @@
         <v>90009</v>
       </c>
       <c r="CC211">
-        <v>-3.1</v>
+        <v>1.5</v>
       </c>
       <c r="CD211">
-        <v>1.9</v>
+        <v>28.7</v>
       </c>
       <c r="CE211">
-        <v>10.1</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="212" spans="1:83" x14ac:dyDescent="0.3">
@@ -20457,13 +20457,13 @@
         <v>123051</v>
       </c>
       <c r="CC212">
-        <v>1.9</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="CD212">
-        <v>2.2000000000000002</v>
+        <v>104.8</v>
       </c>
       <c r="CE212">
-        <v>18.3</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="213" spans="1:83" x14ac:dyDescent="0.3">
@@ -20561,10 +20561,10 @@
         <v>135078</v>
       </c>
       <c r="CC213">
-        <v>3.7</v>
+        <v>1.47</v>
       </c>
       <c r="CD213">
-        <v>1.3</v>
+        <v>85.3</v>
       </c>
       <c r="CE213">
         <v>33.700000000000003</v>
@@ -20665,13 +20665,13 @@
         <v>135732</v>
       </c>
       <c r="CC214">
-        <v>1.9</v>
+        <v>4.25</v>
       </c>
       <c r="CD214">
-        <v>0</v>
+        <v>50.4</v>
       </c>
       <c r="CE214">
-        <v>15.3</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="215" spans="1:83" x14ac:dyDescent="0.3">
@@ -20769,13 +20769,13 @@
         <v>135496</v>
       </c>
       <c r="CC215">
-        <v>3.5</v>
+        <v>5.37</v>
       </c>
       <c r="CD215">
-        <v>2.7</v>
+        <v>80</v>
       </c>
       <c r="CE215">
-        <v>17.3</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="216" spans="1:83" x14ac:dyDescent="0.3">
@@ -20873,13 +20873,13 @@
         <v>132030</v>
       </c>
       <c r="CC216">
-        <v>9.5</v>
+        <v>7.13</v>
       </c>
       <c r="CD216">
-        <v>0</v>
+        <v>89.3</v>
       </c>
       <c r="CE216">
-        <v>17.600000000000001</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="217" spans="1:83" x14ac:dyDescent="0.3">
@@ -20977,13 +20977,13 @@
         <v>136368</v>
       </c>
       <c r="CC217">
-        <v>10</v>
+        <v>9.6199999999999992</v>
       </c>
       <c r="CD217">
-        <v>2.8</v>
+        <v>79.7</v>
       </c>
       <c r="CE217">
-        <v>18.2</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="218" spans="1:83" x14ac:dyDescent="0.3">
@@ -21081,13 +21081,13 @@
         <v>143329</v>
       </c>
       <c r="CC218">
-        <v>8.1999999999999993</v>
+        <v>8.4</v>
       </c>
       <c r="CD218">
-        <v>15.2</v>
+        <v>144</v>
       </c>
       <c r="CE218">
-        <v>31.5</v>
+        <v>34.799999999999997</v>
       </c>
     </row>
     <row r="219" spans="1:83" x14ac:dyDescent="0.3">
@@ -21185,13 +21185,13 @@
         <v>135168</v>
       </c>
       <c r="CC219">
-        <v>5.9</v>
+        <v>8.7899999999999991</v>
       </c>
       <c r="CD219">
-        <v>8.6999999999999993</v>
+        <v>91.4</v>
       </c>
       <c r="CE219">
-        <v>27</v>
+        <v>49</v>
       </c>
     </row>
     <row r="220" spans="1:83" x14ac:dyDescent="0.3">
@@ -21289,13 +21289,13 @@
         <v>147235</v>
       </c>
       <c r="CC220">
-        <v>6.2</v>
+        <v>6.86</v>
       </c>
       <c r="CD220">
-        <v>10.199999999999999</v>
+        <v>141.69999999999999</v>
       </c>
       <c r="CE220">
-        <v>21.7</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="221" spans="1:83" x14ac:dyDescent="0.3">
@@ -21393,13 +21393,13 @@
         <v>136670</v>
       </c>
       <c r="CC221">
-        <v>6.2</v>
+        <v>4.54</v>
       </c>
       <c r="CD221">
-        <v>10.3</v>
+        <v>69.2</v>
       </c>
       <c r="CE221">
-        <v>10.199999999999999</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="222" spans="1:83" x14ac:dyDescent="0.3">
@@ -21497,13 +21497,13 @@
         <v>113277</v>
       </c>
       <c r="CC222">
-        <v>3.8</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="CD222">
-        <v>0.2</v>
+        <v>93.6</v>
       </c>
       <c r="CE222">
-        <v>13</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="223" spans="1:83" x14ac:dyDescent="0.3">
@@ -21601,13 +21601,13 @@
         <v>114022</v>
       </c>
       <c r="CC223">
-        <v>0.9</v>
+        <v>1.37</v>
       </c>
       <c r="CD223">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="CE223">
-        <v>10.6</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="224" spans="1:83" x14ac:dyDescent="0.3">
@@ -21705,13 +21705,13 @@
         <v>147078</v>
       </c>
       <c r="CC224">
-        <v>-2.9</v>
+        <v>-0.5</v>
       </c>
       <c r="CD224">
-        <v>2.2999999999999998</v>
+        <v>93.9</v>
       </c>
       <c r="CE224">
-        <v>13.4</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="225" spans="1:83" x14ac:dyDescent="0.3">
@@ -21809,13 +21809,13 @@
         <v>150337</v>
       </c>
       <c r="CC225">
-        <v>4.9000000000000004</v>
+        <v>2.21</v>
       </c>
       <c r="CD225">
-        <v>0.1</v>
+        <v>58.9</v>
       </c>
       <c r="CE225">
-        <v>16.600000000000001</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="226" spans="1:83" x14ac:dyDescent="0.3">
@@ -21940,13 +21940,13 @@
         <v>142406</v>
       </c>
       <c r="CC226">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="CD226">
-        <v>1.1000000000000001</v>
+        <v>54.9</v>
       </c>
       <c r="CE226">
-        <v>18.399999999999999</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="227" spans="1:83" x14ac:dyDescent="0.3">
@@ -22071,13 +22071,13 @@
         <v>145100</v>
       </c>
       <c r="CC227">
-        <v>4.4000000000000004</v>
+        <v>5.35</v>
       </c>
       <c r="CD227">
-        <v>1.3</v>
+        <v>80.599999999999994</v>
       </c>
       <c r="CE227">
-        <v>24.3</v>
+        <v>33.799999999999997</v>
       </c>
     </row>
     <row r="228" spans="1:83" x14ac:dyDescent="0.3">
@@ -22202,13 +22202,13 @@
         <v>144496</v>
       </c>
       <c r="CC228">
-        <v>5.4</v>
+        <v>8.82</v>
       </c>
       <c r="CD228">
-        <v>1.2</v>
+        <v>54.4</v>
       </c>
       <c r="CE228">
-        <v>16.899999999999999</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="229" spans="1:83" x14ac:dyDescent="0.3">
@@ -22333,10 +22333,10 @@
         <v>147844</v>
       </c>
       <c r="CC229">
-        <v>8.9</v>
+        <v>8.36</v>
       </c>
       <c r="CD229">
-        <v>1.5</v>
+        <v>120.7</v>
       </c>
       <c r="CE229">
         <v>35.200000000000003</v>
@@ -22584,13 +22584,13 @@
         <v>2101</v>
       </c>
       <c r="CC230">
-        <v>8.4</v>
+        <v>10.28</v>
       </c>
       <c r="CD230">
-        <v>3</v>
+        <v>100.7</v>
       </c>
       <c r="CE230">
-        <v>22.3</v>
+        <v>32.299999999999997</v>
       </c>
     </row>
     <row r="231" spans="1:83" x14ac:dyDescent="0.3">
@@ -22835,13 +22835,13 @@
         <v>5239</v>
       </c>
       <c r="CC231">
-        <v>12.5</v>
+        <v>8.8699999999999992</v>
       </c>
       <c r="CD231">
-        <v>0.9</v>
+        <v>120.3</v>
       </c>
       <c r="CE231">
-        <v>20.8</v>
+        <v>36.200000000000003</v>
       </c>
     </row>
     <row r="232" spans="1:83" x14ac:dyDescent="0.3">
@@ -23086,13 +23086,13 @@
         <v>3362</v>
       </c>
       <c r="CC232">
-        <v>6.7</v>
+        <v>5.28</v>
       </c>
       <c r="CD232">
-        <v>1.5</v>
+        <v>125</v>
       </c>
       <c r="CE232">
-        <v>25</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="233" spans="1:83" x14ac:dyDescent="0.3">
@@ -23337,13 +23337,13 @@
         <v>855</v>
       </c>
       <c r="CC233">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="CD233">
-        <v>0.5</v>
+        <v>90.6</v>
       </c>
       <c r="CE233">
-        <v>9</v>
+        <v>33.700000000000003</v>
       </c>
     </row>
     <row r="234" spans="1:83" x14ac:dyDescent="0.3">
@@ -23561,13 +23561,13 @@
         <v>543</v>
       </c>
       <c r="CC234">
-        <v>1.8</v>
+        <v>4.01</v>
       </c>
       <c r="CD234">
-        <v>7.9</v>
+        <v>74.7</v>
       </c>
       <c r="CE234">
-        <v>24.1</v>
+        <v>33.299999999999997</v>
       </c>
     </row>
     <row r="235" spans="1:83" x14ac:dyDescent="0.3">
@@ -23785,13 +23785,13 @@
         <v>268</v>
       </c>
       <c r="CC235">
-        <v>4.4000000000000004</v>
+        <v>0.74</v>
       </c>
       <c r="CD235">
-        <v>0</v>
+        <v>60.1</v>
       </c>
       <c r="CE235">
-        <v>27.4</v>
+        <v>34.700000000000003</v>
       </c>
     </row>
     <row r="236" spans="1:83" x14ac:dyDescent="0.3">
@@ -23991,13 +23991,13 @@
         <v>888</v>
       </c>
       <c r="CC236">
-        <v>3.5</v>
+        <v>-0.52</v>
       </c>
       <c r="CD236">
-        <v>5.7</v>
+        <v>69.2</v>
       </c>
       <c r="CE236">
-        <v>44.3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="237" spans="1:83" x14ac:dyDescent="0.3">
@@ -24215,13 +24215,13 @@
         <v>973</v>
       </c>
       <c r="CC237">
-        <v>0.6</v>
+        <v>0.37</v>
       </c>
       <c r="CD237">
-        <v>3.5</v>
+        <v>74.099999999999994</v>
       </c>
       <c r="CE237">
-        <v>17.600000000000001</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="238" spans="1:83" x14ac:dyDescent="0.3">
@@ -24454,13 +24454,13 @@
         <v>2604</v>
       </c>
       <c r="CC238">
-        <v>-0.9</v>
+        <v>1.39</v>
       </c>
       <c r="CD238">
-        <v>0</v>
+        <v>50.4</v>
       </c>
       <c r="CE238">
-        <v>10.7</v>
+        <v>33.200000000000003</v>
       </c>
     </row>
     <row r="239" spans="1:83" x14ac:dyDescent="0.3">
@@ -24705,13 +24705,13 @@
         <v>1557</v>
       </c>
       <c r="CC239">
-        <v>2.7</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="CD239">
-        <v>1.2</v>
+        <v>100.2</v>
       </c>
       <c r="CE239">
-        <v>29.5</v>
+        <v>40.799999999999997</v>
       </c>
     </row>
     <row r="240" spans="1:83" x14ac:dyDescent="0.3">
@@ -24956,13 +24956,13 @@
         <v>2667</v>
       </c>
       <c r="CC240">
-        <v>3.8</v>
+        <v>5.18</v>
       </c>
       <c r="CD240">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="CE240">
-        <v>14.2</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="241" spans="1:83" x14ac:dyDescent="0.3">
@@ -25207,13 +25207,13 @@
         <v>2371</v>
       </c>
       <c r="CC241">
-        <v>5.3</v>
+        <v>7.77</v>
       </c>
       <c r="CD241">
-        <v>1.5</v>
+        <v>73.099999999999994</v>
       </c>
       <c r="CE241">
-        <v>18.8</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="242" spans="1:83" x14ac:dyDescent="0.3">
@@ -25458,13 +25458,13 @@
         <v>4800</v>
       </c>
       <c r="CC242">
-        <v>11.5</v>
+        <v>9.0500000000000007</v>
       </c>
       <c r="CD242">
-        <v>0.3</v>
+        <v>115.6</v>
       </c>
       <c r="CE242">
-        <v>11.9</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="243" spans="1:83" x14ac:dyDescent="0.3">
@@ -25709,13 +25709,13 @@
         <v>7000</v>
       </c>
       <c r="CC243">
-        <v>10.3</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="CD243">
-        <v>4.5</v>
+        <v>92.2</v>
       </c>
       <c r="CE243">
-        <v>31.6</v>
+        <v>35.200000000000003</v>
       </c>
     </row>
     <row r="244" spans="1:83" x14ac:dyDescent="0.3">
@@ -25960,13 +25960,13 @@
         <v>1792</v>
       </c>
       <c r="CC244">
-        <v>11.3</v>
+        <v>6.51</v>
       </c>
       <c r="CD244">
-        <v>2.9</v>
+        <v>111.6</v>
       </c>
       <c r="CE244">
-        <v>22.9</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="245" spans="1:83" x14ac:dyDescent="0.3">
@@ -26205,13 +26205,13 @@
         <v>1686</v>
       </c>
       <c r="CC245">
-        <v>5</v>
+        <v>3.64</v>
       </c>
       <c r="CD245">
-        <v>0.1</v>
+        <v>139.69999999999999</v>
       </c>
       <c r="CE245">
-        <v>26.2</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="246" spans="1:83" x14ac:dyDescent="0.3">
@@ -26429,13 +26429,13 @@
         <v>595</v>
       </c>
       <c r="CC246">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="CD246">
-        <v>0.5</v>
+        <v>126.5</v>
       </c>
       <c r="CE246">
-        <v>9.4</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="247" spans="1:83" x14ac:dyDescent="0.3">
@@ -26653,13 +26653,13 @@
         <v>162</v>
       </c>
       <c r="CC247">
-        <v>0.5</v>
+        <v>-2.93</v>
       </c>
       <c r="CD247">
-        <v>0.3</v>
+        <v>38.200000000000003</v>
       </c>
       <c r="CE247">
-        <v>10</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="248" spans="1:83" x14ac:dyDescent="0.3">
@@ -26877,13 +26877,13 @@
         <v>296</v>
       </c>
       <c r="CC248">
-        <v>-5</v>
+        <v>0.37</v>
       </c>
       <c r="CD248">
-        <v>0.3</v>
+        <v>97.4</v>
       </c>
       <c r="CE248">
-        <v>11.2</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="249" spans="1:83" x14ac:dyDescent="0.3">
@@ -27101,13 +27101,13 @@
         <v>189</v>
       </c>
       <c r="CC249">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="CD249">
-        <v>3.3</v>
+        <v>51.2</v>
       </c>
       <c r="CE249">
-        <v>6.6</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="250" spans="1:83" x14ac:dyDescent="0.3">
@@ -27340,13 +27340,13 @@
         <v>208</v>
       </c>
       <c r="CC250">
-        <v>4.9000000000000004</v>
+        <v>1.32</v>
       </c>
       <c r="CD250">
-        <v>0.7</v>
+        <v>99.1</v>
       </c>
       <c r="CE250">
-        <v>22</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="251" spans="1:83" x14ac:dyDescent="0.3">
@@ -27585,13 +27585,13 @@
         <v>534</v>
       </c>
       <c r="CC251">
-        <v>-4.3</v>
+        <v>5.24</v>
       </c>
       <c r="CD251">
-        <v>1</v>
+        <v>77.400000000000006</v>
       </c>
       <c r="CE251">
-        <v>14.9</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="252" spans="1:83" x14ac:dyDescent="0.3">
@@ -27836,13 +27836,13 @@
         <v>2291</v>
       </c>
       <c r="CC252">
-        <v>8.6999999999999993</v>
+        <v>7.27</v>
       </c>
       <c r="CD252">
-        <v>8.3000000000000007</v>
+        <v>100.8</v>
       </c>
       <c r="CE252">
-        <v>17.8</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="253" spans="1:83" x14ac:dyDescent="0.3">
@@ -28087,13 +28087,13 @@
         <v>1654</v>
       </c>
       <c r="CC253">
-        <v>4</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="CD253">
-        <v>5.8</v>
+        <v>113</v>
       </c>
       <c r="CE253">
-        <v>25.6</v>
+        <v>33.299999999999997</v>
       </c>
     </row>
     <row r="254" spans="1:83" x14ac:dyDescent="0.3">
@@ -28338,13 +28338,13 @@
         <v>2851</v>
       </c>
       <c r="CC254">
-        <v>14.1</v>
+        <v>10.4</v>
       </c>
       <c r="CD254">
-        <v>0.1</v>
+        <v>139</v>
       </c>
       <c r="CE254">
-        <v>14.9</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="255" spans="1:83" x14ac:dyDescent="0.3">
@@ -28589,13 +28589,13 @@
         <v>1582</v>
       </c>
       <c r="CC255">
-        <v>11.5</v>
+        <v>7.45</v>
       </c>
       <c r="CD255">
-        <v>4.5999999999999996</v>
+        <v>127</v>
       </c>
       <c r="CE255">
-        <v>25</v>
+        <v>37.799999999999997</v>
       </c>
     </row>
     <row r="256" spans="1:83" x14ac:dyDescent="0.3">
@@ -28840,13 +28840,13 @@
         <v>1697</v>
       </c>
       <c r="CC256">
-        <v>10.1</v>
+        <v>7.49</v>
       </c>
       <c r="CD256">
-        <v>2.4</v>
+        <v>89</v>
       </c>
       <c r="CE256">
-        <v>11.9</v>
+        <v>39.700000000000003</v>
       </c>
     </row>
     <row r="257" spans="1:83" x14ac:dyDescent="0.3">
@@ -29079,13 +29079,13 @@
         <v>664</v>
       </c>
       <c r="CC257">
-        <v>2.9</v>
+        <v>5.96</v>
       </c>
       <c r="CD257">
-        <v>14.7</v>
+        <v>66.3</v>
       </c>
       <c r="CE257">
-        <v>27</v>
+        <v>32.799999999999997</v>
       </c>
     </row>
     <row r="258" spans="1:83" x14ac:dyDescent="0.3">
@@ -29303,13 +29303,13 @@
         <v>166</v>
       </c>
       <c r="CC258">
-        <v>6</v>
+        <v>2.64</v>
       </c>
       <c r="CD258">
-        <v>0.5</v>
+        <v>95.5</v>
       </c>
       <c r="CE258">
-        <v>6.2</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="259" spans="1:83" x14ac:dyDescent="0.3">
@@ -29527,13 +29527,13 @@
         <v>165</v>
       </c>
       <c r="CC259">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="CD259">
-        <v>3.5</v>
+        <v>78.8</v>
       </c>
       <c r="CE259">
-        <v>16</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="260" spans="1:83" x14ac:dyDescent="0.3">
@@ -29751,13 +29751,13 @@
         <v>750</v>
       </c>
       <c r="CC260">
-        <v>2.8</v>
+        <v>1.67</v>
       </c>
       <c r="CD260">
-        <v>0</v>
+        <v>39.799999999999997</v>
       </c>
       <c r="CE260">
-        <v>8.6999999999999993</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="261" spans="1:83" x14ac:dyDescent="0.3">
@@ -29975,13 +29975,13 @@
         <v>115</v>
       </c>
       <c r="CC261">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="CD261">
-        <v>2.7</v>
+        <v>31</v>
       </c>
       <c r="CE261">
-        <v>3.2</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="262" spans="1:83" x14ac:dyDescent="0.3">
@@ -30199,13 +30199,13 @@
         <v>403</v>
       </c>
       <c r="CC262">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="CD262">
-        <v>0.8</v>
+        <v>77.400000000000006</v>
       </c>
       <c r="CE262">
-        <v>22.7</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="263" spans="1:83" x14ac:dyDescent="0.3">
@@ -30423,13 +30423,13 @@
         <v>473</v>
       </c>
       <c r="CC263">
-        <v>4.0999999999999996</v>
+        <v>5.25</v>
       </c>
       <c r="CD263">
-        <v>2.8</v>
+        <v>87</v>
       </c>
       <c r="CE263">
-        <v>27</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="264" spans="1:83" x14ac:dyDescent="0.3">
@@ -30647,13 +30647,13 @@
         <v>1440</v>
       </c>
       <c r="CC264">
-        <v>3.9</v>
+        <v>6.35</v>
       </c>
       <c r="CD264">
-        <v>5.7</v>
+        <v>159.19999999999999</v>
       </c>
       <c r="CE264">
-        <v>25.4</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
   </sheetData>
